--- a/AAII_Financials/Quarterly/SEOAY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SEOAY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="431" uniqueCount="92">
   <si>
     <t>SEOAY</t>
   </si>
@@ -656,177 +656,181 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="43" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -869,86 +873,89 @@
       <c r="P8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="Q8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R8" s="3">
         <v>3172200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>3202100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>3323100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>3035800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2947700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2775200</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2742300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>2323300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>2147400</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>2157800</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>2306200</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>2491900</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>2814600</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>2942400</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>3068100</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>3152000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>3144100</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>2863100</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>2925100</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>2831700</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>2817300</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>2815100</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>2836400</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>2931000</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>2861700</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>2808900</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -991,86 +998,89 @@
       <c r="P9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="Q9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R9" s="3">
         <v>2627200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>2439100</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>2602700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>2345800</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>2329700</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>2180700</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>2183700</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>1903800</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>1868100</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>1803900</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>1922200</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>2065100</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>2445700</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>2424300</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>2503400</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>2512000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>2572800</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>2225200</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>2333300</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>2179500</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>1934300</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>1910700</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>1950000</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>2019000</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>2006000</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>1946200</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -1113,86 +1123,89 @@
       <c r="P10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="Q10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R10" s="3">
         <v>544900</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>763000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>720300</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>690100</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>617900</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>594400</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>558600</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>419500</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>279300</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>353900</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>384000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>426800</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>368900</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>518200</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>564700</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>640000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>571300</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>638000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>591800</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>652200</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>883000</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>904300</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>886400</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>912100</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>855700</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>862800</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1235,8 +1248,9 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1357,8 +1371,11 @@
       <c r="AP12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1479,8 +1496,11 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1523,68 +1543,68 @@
       <c r="P14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="Q14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R14" s="3">
         <v>-241500</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
-      </c>
       <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
         <v>71800</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>87900</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>-354500</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>-6500</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>40200</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>110200</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>-209500</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>14500</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>-69800</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>-132100</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>-513700</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>36700</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>5900</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>19100</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>20100</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>22200</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>18700</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>15400</v>
-      </c>
-      <c r="AK14" s="3">
-        <v>22400</v>
       </c>
       <c r="AL14" s="3">
         <v>22400</v>
@@ -1593,16 +1613,19 @@
         <v>22400</v>
       </c>
       <c r="AN14" s="3">
+        <v>22400</v>
+      </c>
+      <c r="AO14" s="3">
         <v>14100</v>
       </c>
-      <c r="AO14" s="3">
+      <c r="AP14" s="3">
         <v>237100</v>
       </c>
-      <c r="AP14" s="3">
+      <c r="AQ14" s="3">
         <v>25800</v>
       </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1645,86 +1668,89 @@
       <c r="P15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="Q15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R15" s="3">
         <v>126300</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>141600</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>142500</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>146500</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>158300</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>146500</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>142800</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>141900</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>149600</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>140100</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>148400</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>155800</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>171600</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>160500</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>157600</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>159100</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>134900</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>135100</v>
-      </c>
-      <c r="AI15" s="3">
-        <v>132900</v>
       </c>
       <c r="AJ15" s="3">
         <v>132900</v>
       </c>
       <c r="AK15" s="3">
+        <v>132900</v>
+      </c>
+      <c r="AL15" s="3">
         <v>145900</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>139100</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AN15" s="3">
         <v>133500</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AO15" s="3">
         <v>166700</v>
       </c>
-      <c r="AO15" s="3">
+      <c r="AP15" s="3">
         <v>71600</v>
       </c>
-      <c r="AP15" s="3">
+      <c r="AQ15" s="3">
         <v>152600</v>
       </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1764,8 +1790,9 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1808,86 +1835,89 @@
       <c r="P17" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="Q17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R17" s="3">
         <v>2391300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2649900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2888900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2608300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2038100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2359500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2549800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2159000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1859200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2007300</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>2059600</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>2196100</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>2019600</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>2734200</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>2901000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>2777600</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>2723000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>2461100</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>2577000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>2442000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>2552500</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>2512100</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>2606400</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>2704500</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>2691500</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>2578900</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1930,86 +1960,89 @@
       <c r="P18" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="Q18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R18" s="3">
         <v>780900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>552200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>434200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>427500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>909600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>415700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>192600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>164300</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>288200</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>150500</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>246500</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>295800</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>795000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>208200</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>167000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>374400</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>421100</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>402100</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>348100</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>389800</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>264800</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>302900</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>230000</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>226500</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>170200</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>230100</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2052,8 +2085,9 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -2096,86 +2130,89 @@
       <c r="P20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="Q20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R20" s="3">
         <v>-43200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-68100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-31600</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-21700</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-49900</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-39800</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-31700</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-36700</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-28900</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-31100</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-39300</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-59800</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-39700</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-67400</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-57600</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-37100</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-48500</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-64200</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-65900</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-24200</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-30300</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>-51600</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>-67300</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>-34000</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>-81000</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>-41100</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -2218,86 +2255,89 @@
       <c r="P21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="Q21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R21" s="3">
         <v>1295900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>484200</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>398200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>552300</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1467900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>376900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>156600</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>269500</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>732100</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>118300</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>205100</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>391800</v>
       </c>
-      <c r="AC21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AE21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF21" s="3">
         <v>110600</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>496400</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>363200</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>338900</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>282200</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>498500</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>241200</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>256900</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>136900</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>359200</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>403800</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>245300</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2340,8 +2380,8 @@
       <c r="P22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
+      <c r="Q22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R22" s="3">
         <v>0</v>
@@ -2418,8 +2458,11 @@
       <c r="AP22" s="3">
         <v>0</v>
       </c>
+      <c r="AQ22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -2462,86 +2505,89 @@
       <c r="P23" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="Q23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R23" s="3">
         <v>737700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>484200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>402600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>405800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>859700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>375800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>160800</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>127600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>259300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>119400</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>207300</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>236000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>755300</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>140900</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>109400</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>337300</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>372600</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>337800</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>282200</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>365600</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>234500</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>251300</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>162700</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>192500</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>89200</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>189000</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2584,86 +2630,89 @@
       <c r="P24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="Q24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R24" s="3">
         <v>90800</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>87500</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>77300</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>95500</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>191900</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>53800</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-59200</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-20400</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>22900</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>29100</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>50200</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>66600</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>148300</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>69800</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>48200</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>67000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>18900</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>111900</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>48300</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>65900</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>40400</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>37000</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>2200</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>66900</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>23500</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>49300</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2784,8 +2833,11 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2828,86 +2880,89 @@
       <c r="P26" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="Q26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R26" s="3">
         <v>646800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>396600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>325300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>310300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>667800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>322000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>220100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>148000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>236400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>90300</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>157100</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>169400</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>607100</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>71000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>61200</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>270300</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>353700</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>226000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>233900</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>299800</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>194100</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>214300</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>160400</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>125600</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>65700</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>139700</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2950,86 +3005,89 @@
       <c r="P27" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="Q27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R27" s="3">
         <v>649100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>402000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>329700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>313600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>667800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>324100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>217900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>147000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>238400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>91300</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>160400</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>171600</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>607100</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>85700</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>69400</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>277500</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>359600</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>237000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>242700</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>300900</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>195200</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>214300</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>163800</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>133800</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>106800</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>151400</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3150,8 +3208,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3194,8 +3255,8 @@
       <c r="P29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q29" s="3">
-        <v>0</v>
+      <c r="Q29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R29" s="3">
         <v>0</v>
@@ -3272,8 +3333,11 @@
       <c r="AP29" s="3">
         <v>0</v>
       </c>
+      <c r="AQ29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3394,8 +3458,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3516,8 +3583,11 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3560,86 +3630,89 @@
       <c r="P32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="Q32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R32" s="3">
         <v>43200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>68100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>31600</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>21700</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>49900</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>39800</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>31700</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>36700</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>28900</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>31100</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>39300</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>59800</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>39700</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>67400</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>57600</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>37100</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>48500</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>64200</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>65900</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>24200</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>30300</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>51600</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>67300</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>34000</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>81000</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>41100</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -3682,86 +3755,89 @@
       <c r="P33" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="Q33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R33" s="3">
         <v>649100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>402000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>329700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>313600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>667800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>324100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>217900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>147000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>238400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>91300</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>160400</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>171600</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>607100</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>85700</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>69400</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>277500</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>359600</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>237000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>242700</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>300900</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>195200</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>214300</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>163800</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>133800</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>106800</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>151400</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3882,8 +3958,11 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -3926,213 +4005,219 @@
       <c r="P35" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="Q35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R35" s="3">
         <v>649100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>402000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>329700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>313600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>667800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>324100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>217900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>147000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>238400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>91300</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>160400</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>171600</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>607100</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>85700</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>69400</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>277500</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>359600</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>237000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>242700</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>300900</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>195200</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>214300</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>163800</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>133800</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>106800</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>151400</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4175,8 +4260,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4219,130 +4305,134 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1780000</v>
+      </c>
+      <c r="E41" s="3">
         <v>1165700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1423000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2614100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1843800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1793100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2069600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2229500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2222200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2264500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2723600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>2198300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>2153900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1365700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>2123300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1755100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1477600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1066600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1605600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1369800</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1389200</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1295400</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1656700</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1415700</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1158500</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>853600</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1022700</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>873400</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>979900</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>1463000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>1336700</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>1113100</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>690600</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>754300</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>681000</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>469000</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>559900</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>1094000</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>1118600</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>916700</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4463,252 +4553,261 @@
       <c r="AP42" s="3">
         <v>0</v>
       </c>
+      <c r="AQ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1278400</v>
+      </c>
+      <c r="E43" s="3">
         <v>1240600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1054400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1314100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1340000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1270000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>993900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1344000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1299700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1304300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1386100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1398200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1528400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1698200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1655900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1810200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1941200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1804400</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1645700</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1590600</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>1561600</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>1372000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>1157000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>1228900</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>1330900</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>1446400</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>1521100</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>1632900</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>1765800</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>1897200</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>1834700</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>1680200</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>1681000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>1631600</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>1579800</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>1576400</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>1580900</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>1618700</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>1558800</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>1659800</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>2025600</v>
+      </c>
+      <c r="E44" s="3">
         <v>2131900</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>2115800</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>2083800</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>2043500</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1945500</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1731000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1891600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1592200</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1594600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1707700</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1748500</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1922500</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>2067600</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>2004800</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>1908500</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>1870400</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>1756600</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>1602300</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>1580900</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>1415600</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>1370900</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>1266700</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>1351300</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>1488000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>1577400</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>1623900</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>1860800</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>1832800</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>1992900</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>1853600</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>1664700</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>1559200</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>1592100</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>1482100</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>1493400</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>1515800</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>1687900</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>1579900</v>
       </c>
-      <c r="AP44" s="3">
+      <c r="AQ44" s="3">
         <v>1514200</v>
       </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4721,87 +4820,87 @@
       <c r="F45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G45" s="3">
+      <c r="G45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H45" s="3">
         <v>1055800</v>
       </c>
-      <c r="H45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I45" s="3">
+      <c r="I45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J45" s="3">
         <v>1000</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L45" s="3">
         <v>916100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>919200</v>
       </c>
-      <c r="M45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="N45" s="3" t="s">
         <v>8</v>
       </c>
       <c r="O45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P45" s="3">
+      <c r="P45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q45" s="3">
         <v>35900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>72000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>19500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>6500</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>16300</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>34700</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>5400</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>8500</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>6100</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>63800</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>17600</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>26200</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>11300</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>23300</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>13500</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>20000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>25100</v>
       </c>
-      <c r="AG45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AH45" s="3" t="s">
         <v>8</v>
       </c>
@@ -4811,8 +4910,8 @@
       <c r="AJ45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AK45" s="3">
-        <v>0</v>
+      <c r="AK45" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AL45" s="3">
         <v>0</v>
@@ -4829,496 +4928,511 @@
       <c r="AP45" s="3">
         <v>0</v>
       </c>
+      <c r="AQ45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>5084000</v>
+      </c>
+      <c r="E46" s="3">
         <v>4538200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>4670700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>6012000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>6283000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>5008600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>4885600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>5465100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>6030200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>6082600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>5905800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>5345000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>5604800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>5167300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>5855900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>5493200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>5295800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>4643800</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>4888200</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>4546700</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>4374800</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>4044400</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>4144200</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>4013600</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>4003600</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>3888600</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>4191000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>4380600</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>4598500</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>5378100</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>5025000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>4458100</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>3930800</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>3978100</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>3743000</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>3538800</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>3656600</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>4400600</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>4257400</v>
       </c>
-      <c r="AP46" s="3">
+      <c r="AQ46" s="3">
         <v>4090700</v>
       </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>2520300</v>
+      </c>
+      <c r="E47" s="3">
         <v>2110000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>2371700</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>2296100</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>1857900</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>1736900</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1622300</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1790100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1638300</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1814700</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1928800</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1600300</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>1708500</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>1953500</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>2654900</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>2614200</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>1760500</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>1770700</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>1679300</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>1394600</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>1096100</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>994300</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>963500</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>954900</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>952400</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>931500</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>1276000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>1429600</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>1271700</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>2598100</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>2623700</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>2372500</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>2127900</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>2109300</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>2237200</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>2186800</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>2076800</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>2217300</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>2225500</v>
       </c>
-      <c r="AP47" s="3">
+      <c r="AQ47" s="3">
         <v>2027200</v>
       </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>13946100</v>
+      </c>
+      <c r="E48" s="3">
         <v>14101200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>14428800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>14103000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>14055200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>14120200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>13180500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>14204800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>12858700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>12670200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>13794600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>13050400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>13151700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>13469100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>13428500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>13139200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>13493500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>13181700</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>13279100</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>12568500</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>12371200</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>11734100</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>11683500</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>10030300</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>10677800</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>10744500</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>11376400</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>11076400</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>10686400</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>7542000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>6731900</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>6154900</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>6126800</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>6149900</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>6460400</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>6440200</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>6509800</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>7095700</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>7160200</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>7358600</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>521000</v>
+      </c>
+      <c r="E49" s="3">
         <v>553400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>547100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>587800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>628300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>608500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>530100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1036100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1030800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1042200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1013600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1105000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1144100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1220100</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>540500</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>613800</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>667000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>735600</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>588700</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>588000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>559700</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>544100</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>449800</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>489900</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>533500</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>605200</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>593000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>635800</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>630600</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>590900</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>618700</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>569300</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>565500</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>557800</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>536300</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>476800</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>490300</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>521200</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>507100</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>516500</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5439,8 +5553,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5561,130 +5678,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>93700</v>
+      </c>
+      <c r="E52" s="3">
         <v>89900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>82200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>88000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>66900</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>68100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>55900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>58000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>55700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>61500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>65200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>84700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>77500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>38000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>693400</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>704600</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>191500</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>175800</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>190800</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>202500</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>228500</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>160300</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>144600</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>134900</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>165800</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>155800</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>136600</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>156800</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>155300</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>168700</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>199900</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>139600</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>175700</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>186700</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>228900</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>226600</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>270400</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>301700</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>318100</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>293500</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5805,130 +5928,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>22455200</v>
+      </c>
+      <c r="E54" s="3">
         <v>21684500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>22377600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>23323900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>23107500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>21782300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>20501100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>22738100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>21779700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>21906400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>22940200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>21407700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>21919200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>22042600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>23173200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>22565000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>21408400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>20507600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>20626100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>19300200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>18630300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>17477100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>17385700</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>15623500</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>16333100</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>16325700</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>17573000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>17679100</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>17342500</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>16277900</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>15199100</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>13694400</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>12926800</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>12981700</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>13205800</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>12869200</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>13003900</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>14536500</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>14468400</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>14286400</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5971,8 +6100,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -6015,52 +6145,53 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E57" s="3">
+      <c r="E57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F57" s="3">
         <v>2118100</v>
       </c>
-      <c r="F57" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="G57" s="3" t="s">
         <v>8</v>
       </c>
       <c r="H57" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I57" s="3">
+      <c r="I57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J57" s="3">
         <v>1843900</v>
       </c>
-      <c r="J57" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="K57" s="3" t="s">
         <v>8</v>
       </c>
       <c r="L57" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M57" s="3">
+      <c r="M57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N57" s="3">
         <v>1841500</v>
       </c>
-      <c r="N57" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O57" s="3" t="s">
         <v>8</v>
       </c>
       <c r="P57" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q57" s="3">
-        <v>0</v>
+      <c r="Q57" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R57" s="3">
         <v>0</v>
@@ -6137,618 +6268,636 @@
       <c r="AP57" s="3">
         <v>0</v>
       </c>
+      <c r="AQ57" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1292100</v>
+      </c>
+      <c r="E58" s="3">
         <v>1509300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1076700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>2234000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>2475600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1981200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1951500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1775600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1176500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>942900</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1109800</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1220400</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1181200</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1624300</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1213900</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>921800</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>965100</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>666200</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>599500</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>592300</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>913100</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>970800</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>888700</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>497200</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>885800</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>397400</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>1056500</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>430000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>424700</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>385200</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>477900</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>494000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>428200</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>457900</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>1088300</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>1067000</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>1128700</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>1629200</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>1313500</v>
       </c>
-      <c r="AP58" s="3">
+      <c r="AQ58" s="3">
         <v>1460200</v>
       </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>2543100</v>
+      </c>
+      <c r="E59" s="3">
         <v>2718800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>283000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>2657500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>2675300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>2608100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>235000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2522900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>3041900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>3007900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>361400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2330700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2400700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>2745500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>2880900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>2873600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>2883500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>2932800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>2831700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>2533900</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>2319100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>2102800</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1998800</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>2417300</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>1900400</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>2919900</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>2348800</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>2973100</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>2977500</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>3314700</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>3244700</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>2825500</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>2747200</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>2742800</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>2236100</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>2022900</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>2008400</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>2225500</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>2195000</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>2132800</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>3835300</v>
+      </c>
+      <c r="E60" s="3">
         <v>4228100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>3847600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>4891500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>5150900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>4589300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>4380400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>4298500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>4218400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>3950800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>3698500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>3551000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>3581900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>4369800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>4094800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>3795400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>3848600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>3598900</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>3431200</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>3126200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>3232200</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>3073600</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>2887500</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>2914400</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>2786200</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>3317300</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>3405300</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>3403000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>3402100</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>3699800</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>3722600</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>3319500</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>3175400</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>3200700</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>3324500</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>3090000</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>3137100</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>3854800</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>3508500</v>
       </c>
-      <c r="AP60" s="3">
+      <c r="AQ60" s="3">
         <v>3593000</v>
       </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>3547400</v>
+      </c>
+      <c r="E61" s="3">
         <v>3809500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>4176400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>4279000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>4204300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>4219600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>4031500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>4561700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>4359800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>4649900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>5278000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>4426300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>4462900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>3111700</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>3092400</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>3252900</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>3306700</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>3344000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>3591600</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>3731500</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>3724200</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>3696300</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>3812100</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>3599400</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>3942500</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>3549900</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>3773100</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>4297300</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>4497400</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>3942700</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>2679300</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>2484300</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>2375000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>2269600</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>2295600</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>2347200</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>2597400</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>2739700</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>3116500</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>3056600</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>124500</v>
+      </c>
+      <c r="E62" s="3">
         <v>131400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>128000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>157200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>338200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>99400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>94200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>103700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>96400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>96000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>105000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>97400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>101500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>101000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>2138800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>2052200</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1930300</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1948700</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>2040300</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1938400</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>1946700</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>1831300</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>1916000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>1606700</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>1716000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>1548000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>1728900</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>1579000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>1534000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>818200</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>833900</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>736600</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>699400</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>717000</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>792100</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>871800</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>916700</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>936700</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>955500</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>923800</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6869,8 +7018,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6991,8 +7143,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7113,130 +7268,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>9145400</v>
+      </c>
+      <c r="E66" s="3">
         <v>9829400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>9874400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>11031300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>11421000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>10724200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>10159400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>10781800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>10385700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>10391600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>10905300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>9758700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>9901700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>9377400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>9292800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>9068200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>9058400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>8871000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>9045700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>8780000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>8889300</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>8587000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>8599600</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>8106000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>8430600</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>8402800</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>8899200</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>9257200</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>9434700</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>8476300</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>7257100</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>6565900</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>6291500</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>6237700</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>6464900</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>6362800</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>6707300</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>7594600</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>7653200</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>7684900</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7279,8 +7440,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7401,8 +7563,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7523,8 +7688,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7645,8 +7813,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7767,130 +7938,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>8249700</v>
+      </c>
+      <c r="E72" s="3">
         <v>8345400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>8680300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>8242400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>7839100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>7195200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>6972800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>7969000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>7586000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>7585500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>7754000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>7786800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>8066600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>8249700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>8742300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>7992900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>7585100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>7130600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>7209300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>6513100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>6056000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>5598100</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>5501700</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>5533000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>5736000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>5962800</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>6435900</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>5713400</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>5409100</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>5428400</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>5567900</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>4893400</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>4618200</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>4729100</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>4526100</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>4275900</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>4057100</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>4415900</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>4284400</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>4223400</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -8011,8 +8188,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8133,8 +8313,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8255,130 +8438,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>13482200</v>
+      </c>
+      <c r="E76" s="3">
         <v>12027000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>12675800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>12465100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>11861400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>11220300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>10496900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>12074500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>11501100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>11620500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>12142100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>11713600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>12080800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>12698800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>13880400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>13496900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>12349900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>11636600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>11580400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>10520200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>9741000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>8890100</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>8786100</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>7517500</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>7902600</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>7922900</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>8673900</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>8421800</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>7907800</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>7801600</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>7942000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>7128500</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>6635200</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>6743900</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>6740900</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>6506400</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>6296600</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>6941900</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>6815100</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>6601500</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8499,135 +8688,141 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -8670,86 +8865,89 @@
       <c r="P81" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="Q81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R81" s="3">
         <v>649100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>402000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>329700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>313600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>667800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>324100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>217900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>147000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>238400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>91300</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>160400</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>171600</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>607100</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>85700</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>69400</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>277500</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>359600</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>237000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>242700</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>300900</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>195200</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>214300</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>163800</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>133800</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>106800</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>151400</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8792,53 +8990,54 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>143300</v>
+      </c>
+      <c r="E83" s="3">
         <v>127500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>80800</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>140500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>142500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>135900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>-60800</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>154500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>293700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>169500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>94000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>194200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>134900</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>104400</v>
       </c>
-      <c r="Q83" s="3">
-        <v>0</v>
-      </c>
       <c r="R83" s="3">
         <v>0</v>
       </c>
@@ -8914,8 +9113,11 @@
       <c r="AP83" s="3">
         <v>0</v>
       </c>
+      <c r="AQ83" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9036,8 +9238,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9158,8 +9363,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9280,8 +9488,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9402,8 +9613,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9524,130 +9738,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>42300</v>
+      </c>
+      <c r="E89" s="3">
         <v>83000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>306400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>188900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>84600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>163200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>283700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>246500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>268900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>222200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>327200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>219100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>64400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>206400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>403200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>593300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>374300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>352600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>563700</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>477100</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>391500</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>146000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>381000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>398600</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>317500</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>80200</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>753000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>524300</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>544700</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>148300</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>322900</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>451900</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>312900</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>138300</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>529600</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>408400</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>317500</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>97400</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>489500</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>389700</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9690,130 +9910,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-96000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-163700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-221900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-194800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-212600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-258300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-244300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-297800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-253900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-402400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-362600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-204300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-234700</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-274900</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-224000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-150000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-153000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-177000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-192000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-138000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-129100</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-196000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>368000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-152600</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-135300</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-199900</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>358400</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-172700</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-141200</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-147100</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>339500</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-142900</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-137300</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-127400</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>360200</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-154800</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-143600</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-158500</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-258200</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-250000</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9934,8 +10158,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10056,130 +10283,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-94800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-163700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-212500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>757900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-203200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-250800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-195700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-296700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-247500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-482300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-363700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-220200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-199800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-644300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-206000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-218300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-192600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-192000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-160400</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-88300</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-130100</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-98000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-214400</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-152600</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-130900</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-224700</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-249800</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-193500</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-682300</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-149500</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-197500</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-152800</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-94400</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-116400</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-304100</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-218800</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-140200</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-123300</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-77500</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-85700</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10222,86 +10455,87 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E96" s="3">
+      <c r="D96" s="3">
+        <v>117700</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F96" s="3">
         <v>111500</v>
       </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
       <c r="G96" s="3">
+        <v>0</v>
+      </c>
+      <c r="H96" s="3">
         <v>121000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>11900</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>69400</v>
       </c>
-      <c r="J96" s="3">
-        <v>0</v>
-      </c>
       <c r="K96" s="3">
+        <v>0</v>
+      </c>
+      <c r="L96" s="3">
         <v>84600</v>
       </c>
-      <c r="L96" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N96" s="3">
-        <v>0</v>
+      <c r="N96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O96" s="3">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3">
         <v>80800</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>433500</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
-      </c>
       <c r="R96" s="3">
         <v>0</v>
       </c>
       <c r="S96" s="3">
+        <v>0</v>
+      </c>
+      <c r="T96" s="3">
         <v>-81600</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-389500</v>
       </c>
-      <c r="U96" s="3">
-        <v>0</v>
-      </c>
       <c r="V96" s="3">
         <v>0</v>
       </c>
       <c r="W96" s="3">
+        <v>0</v>
+      </c>
+      <c r="X96" s="3">
         <v>-30700</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-212300</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-104700</v>
       </c>
-      <c r="Z96" s="3">
-        <v>0</v>
-      </c>
       <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB96" s="3">
         <v>-128700</v>
       </c>
-      <c r="AB96" s="3">
-        <v>0</v>
-      </c>
       <c r="AC96" s="3">
         <v>0</v>
       </c>
@@ -10312,11 +10546,11 @@
         <v>0</v>
       </c>
       <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG96" s="3">
         <v>-471300</v>
       </c>
-      <c r="AG96" s="3">
-        <v>0</v>
-      </c>
       <c r="AH96" s="3">
         <v>0</v>
       </c>
@@ -10344,8 +10578,11 @@
       <c r="AP96" s="3">
         <v>0</v>
       </c>
+      <c r="AQ96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10466,8 +10703,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10588,8 +10828,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10710,370 +10953,382 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>680900</v>
+      </c>
+      <c r="E100" s="3">
         <v>-153300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-1270400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-181900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-2300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-268100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-92100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-27900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-64300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-137000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>481900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>112200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>901700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-308600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>103000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-77800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>193700</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-704200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-194100</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-432900</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-217900</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-442000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>134600</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>63300</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>149500</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>23700</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-302400</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-491200</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-324700</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>95700</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>45000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>111900</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-294300</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>61500</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-5600</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-278300</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-640700</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-5900</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-219500</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>3500</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-10600</v>
+      </c>
+      <c r="E101" s="3">
         <v>-3200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>20700</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-8900</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-1100</v>
       </c>
-      <c r="H101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I101" s="3">
+      <c r="I101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J101" s="3">
         <v>9900</v>
       </c>
-      <c r="J101" s="3">
-        <v>0</v>
-      </c>
       <c r="K101" s="3">
+        <v>0</v>
+      </c>
+      <c r="L101" s="3">
         <v>8700</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>7600</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>24600</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-8800</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>31400</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>4400</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>25500</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-9700</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>32600</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>4300</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>16300</v>
       </c>
-      <c r="V101" s="3">
-        <v>0</v>
-      </c>
       <c r="W101" s="3">
+        <v>0</v>
+      </c>
+      <c r="X101" s="3">
         <v>4200</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-1000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-3000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-4200</v>
-      </c>
-      <c r="AA101" s="3">
-        <v>-1100</v>
       </c>
       <c r="AB101" s="3">
         <v>-1100</v>
       </c>
       <c r="AC101" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="AD101" s="3">
         <v>1200</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>6100</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-2400</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>17900</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>2400</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-8900</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>6600</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>4400</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>-6700</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>-3400</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>-18000</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>2300</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>11700</v>
       </c>
-      <c r="AP101" s="3">
+      <c r="AQ101" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>628400</v>
+      </c>
+      <c r="E102" s="3">
         <v>-230600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-1160000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>757900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-131500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-358800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>16600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-87000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-43900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-397000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>455400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>111100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>775100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-738800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>325600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>287500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>408000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-539200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>225500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-44200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>47600</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-395000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>298200</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>305100</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>334900</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-121900</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>197300</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-162900</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-464700</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>112400</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>172700</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>402100</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-69200</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>87800</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>213200</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-92000</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-481300</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-29300</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>204200</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>309900</v>
       </c>
     </row>
